--- a/data/trans_orig/IP16A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Estudios-trans_orig.xlsx
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>29852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21420</t>
+          <t>20919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>52327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66059</t>
+          <t>66150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53260</t>
+          <t>52944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69447</t>
+          <t>69534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108929</t>
+          <t>108438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131660</t>
+          <t>129895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>31500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>48090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>58472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79438</t>
+          <t>79929</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20699</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30473</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44570</t>
+          <t>43632</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57544</t>
+          <t>57493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31266</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88690</t>
+          <t>89801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107012</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89414</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109213</t>
+          <t>109578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183996</t>
+          <t>182190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211302</t>
+          <t>210777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>38314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58107</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49361</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>69664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94069</t>
+          <t>94594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121375</t>
+          <t>123181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>43009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58016</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40482</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54810</t>
+          <t>55179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86706</t>
+          <t>88361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107295</t>
+          <t>107673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39916</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30810</t>
+          <t>30441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>45597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>80238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38551</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>19537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31385</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87247</t>
+          <t>86885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59106</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77262</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>157678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40214</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58280</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46014</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64170</t>
+          <t>64373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92296</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116583</t>
+          <t>118214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>24106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57172</t>
+          <t>56844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100031</t>
+          <t>97759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60404</t>
+          <t>60191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80902</t>
+          <t>80760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127656</t>
+          <t>127060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175164</t>
+          <t>179940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63671</t>
+          <t>63999</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59620</t>
+          <t>59833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65703</t>
+          <t>60927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113211</t>
+          <t>113807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,25%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>29210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33204</t>
+          <t>33396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42760</t>
+          <t>43331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59474</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>22214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45393</t>
+          <t>44822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133075</t>
+          <t>131950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119965</t>
+          <t>120047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189045</t>
+          <t>191488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244269</t>
+          <t>243782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>45765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87475</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115647</t>
+          <t>116134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170871</t>
+          <t>168428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A01-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,47 +723,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,47 +1066,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,47 +1409,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,47 +1752,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11307</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7575</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14317</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14095</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10176</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17499</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10112</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17380</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11307</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7582</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14443</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20249</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29852</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3790</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10532</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8966</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5562</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12885</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5681</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12949</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6800</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3664</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10525</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20919</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>23061</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61205</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>52380</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>69601</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59559</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52327</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>66150</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>51711</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>65966</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>68,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61205</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>52944</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>69534</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>60,58%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108438</t>
+          <t>109583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129895</t>
+          <t>132188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39829</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31433</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48654</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>27774</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21183</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35006</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21367</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>35622</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>31,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39829</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31500</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48090</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>39,42%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58472</t>
+          <t>56179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79929</t>
+          <t>78784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>87333</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87333</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87333</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>26435</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20979</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30779</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>25033</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20163</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29043</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19244</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>29220</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>68,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>26435</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21600</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>31348</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57493</t>
+          <t>58073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12998</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8654</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18454</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7361</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16241</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7184</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17160</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>31,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12998</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8085</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>17833</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32204</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>98947</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>88618</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>108340</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>55,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>98686</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>89801</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>108483</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>89108</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>107709</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>98947</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>88910</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>109578</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182190</t>
+          <t>184488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210777</t>
+          <t>211108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>59627</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50234</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69956</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>48111</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38314</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56996</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39088</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>57689</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>59627</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>48996</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>69664</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>37,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94594</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123181</t>
+          <t>120883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146797</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146797</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146797</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8153</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9406</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12471</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12434</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>59,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6439</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8120</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>73,28%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5384</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6285</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9815</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9743</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5190</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39717</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55059</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>46,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>64,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>50483</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43009</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57028</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42939</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57327</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>60,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>47551</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>40023</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>55179</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>55,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88361</t>
+          <t>88000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107673</t>
+          <t>109424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30561</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45903</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>35,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>32496</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25951</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39970</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25652</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40040</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>39,16%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>48,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30441</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>45597</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>44,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60926</t>
+          <t>59175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80238</t>
+          <t>80599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13990</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18167</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>18324</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13496</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22281</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14006</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22492</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13990</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9729</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18515</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>48,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14880</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10703</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19664</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>51,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10468</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6511</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15296</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14786</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>14880</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>10355</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19141</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>51,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>54,86%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67979</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58624</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77455</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>62,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>78212</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>68501</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>86885</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>68124</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>86669</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>61,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>53,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>68,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>67979</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>58903</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>76857</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132523</t>
+          <t>133087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157678</t>
+          <t>158295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55297</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>64652</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>49249</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>40576</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>58960</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40792</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>59337</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>38,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>46,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>55297</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>46419</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>64373</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>44,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118214</t>
+          <t>117650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4806</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11129</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,95%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5266</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10089</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2791</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>65,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5141</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14037</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>65,42%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64911</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54239</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74597</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>60,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>74156</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56844</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>97759</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>61,37%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>47,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71508</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60191</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80760</t>
+          <t>56935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>145664</t>
+          <t>113261</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127060</t>
+          <t>100164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179940</t>
+          <t>124536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33315</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53673</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>46687</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23084</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63999</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>38,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>44334</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>35749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59833</t>
+          <t>52635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>95203</t>
+          <t>87335</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60927</t>
+          <t>76060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113807</t>
+          <t>100432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25089</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18358</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30917</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24596</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19428</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29210</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>59,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27379</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33396</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>49486</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43331</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60265</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18030</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12202</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24761</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17046</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12432</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22214</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>40,94%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25182</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27888</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44822</t>
+          <t>41830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>98162</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>87974</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>110339</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>66,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>104018</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>85806</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>131950</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95069</t>
+          <t>67490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120047</t>
+          <t>87349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>211579</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191488</t>
+          <t>161358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243782</t>
+          <t>190697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>66790</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54613</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76978</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>46,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>73697</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45765</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91909</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>65014</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>55643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87132</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>148337</t>
+          <t>131804</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116134</t>
+          <t>117247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168428</t>
+          <t>146586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
